--- a/fmt/tests/bank_isabel_demo.xlsx
+++ b/fmt/tests/bank_isabel_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FA6880-7ACB-47A4-AA0A-24D0C82B8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16178CC4-B7A5-46FA-B221-B089674FAEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="15435" tabRatio="139" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -142,9 +142,6 @@
     <t>BE04 2332 4197 3931</t>
   </si>
   <si>
-    <t>BE04456595434922</t>
-  </si>
-  <si>
     <t>SAVINGS ACCOUNT</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>+++700/0000/00145+++</t>
+  </si>
+  <si>
+    <t>BE53456595434922</t>
   </si>
 </sst>
 </file>
@@ -715,19 +715,19 @@
         <v>32</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U2" t="s">
         <v>32</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="s">
         <v>32</v>
@@ -747,7 +747,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>38</v>
@@ -756,7 +756,7 @@
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
@@ -804,13 +804,13 @@
         <v>32</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U3" t="s">
         <v>32</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>38</v>
